--- a/artfynd/A 23853-2025 artfynd.xlsx
+++ b/artfynd/A 23853-2025 artfynd.xlsx
@@ -779,7 +779,7 @@
         <v>125753826</v>
       </c>
       <c r="B3" t="n">
-        <v>103755</v>
+        <v>103762</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 23853-2025 artfynd.xlsx
+++ b/artfynd/A 23853-2025 artfynd.xlsx
@@ -779,7 +779,7 @@
         <v>125753826</v>
       </c>
       <c r="B3" t="n">
-        <v>103762</v>
+        <v>103765</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 23853-2025 artfynd.xlsx
+++ b/artfynd/A 23853-2025 artfynd.xlsx
@@ -779,7 +779,7 @@
         <v>125753826</v>
       </c>
       <c r="B3" t="n">
-        <v>103765</v>
+        <v>103769</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 23853-2025 artfynd.xlsx
+++ b/artfynd/A 23853-2025 artfynd.xlsx
@@ -779,7 +779,7 @@
         <v>125753826</v>
       </c>
       <c r="B3" t="n">
-        <v>103769</v>
+        <v>103770</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 23853-2025 artfynd.xlsx
+++ b/artfynd/A 23853-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125754047</v>
       </c>
       <c r="B2" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>125753826</v>
       </c>
       <c r="B3" t="n">
-        <v>103770</v>
+        <v>103772</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 23853-2025 artfynd.xlsx
+++ b/artfynd/A 23853-2025 artfynd.xlsx
@@ -779,7 +779,7 @@
         <v>125753826</v>
       </c>
       <c r="B3" t="n">
-        <v>103772</v>
+        <v>103774</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 23853-2025 artfynd.xlsx
+++ b/artfynd/A 23853-2025 artfynd.xlsx
@@ -779,7 +779,7 @@
         <v>125753826</v>
       </c>
       <c r="B3" t="n">
-        <v>103774</v>
+        <v>103778</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 23853-2025 artfynd.xlsx
+++ b/artfynd/A 23853-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125754047</v>
       </c>
       <c r="B2" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>125753826</v>
       </c>
       <c r="B3" t="n">
-        <v>103778</v>
+        <v>103791</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 23853-2025 artfynd.xlsx
+++ b/artfynd/A 23853-2025 artfynd.xlsx
@@ -779,7 +779,7 @@
         <v>125753826</v>
       </c>
       <c r="B3" t="n">
-        <v>103791</v>
+        <v>103794</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 23853-2025 artfynd.xlsx
+++ b/artfynd/A 23853-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,38 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125754047</v>
+        <v>125753970</v>
       </c>
       <c r="B2" t="n">
-        <v>57653</v>
+        <v>80461</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -714,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>598694</v>
+        <v>598607</v>
       </c>
       <c r="R2" t="n">
-        <v>7217177</v>
+        <v>7217342</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -758,6 +757,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125753826</v>
+        <v>125754047</v>
       </c>
       <c r="B3" t="n">
-        <v>103794</v>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,27 +787,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222412</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -815,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>598613</v>
+        <v>598694</v>
       </c>
       <c r="R3" t="n">
-        <v>7217371</v>
+        <v>7217177</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -859,7 +859,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -875,6 +874,108 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>125753826</v>
+      </c>
+      <c r="B4" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Storuman, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>598613</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7217371</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
